--- a/SoTL_Compendium_Contributors.xlsx
+++ b/SoTL_Compendium_Contributors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gla-my.sharepoint.com/personal/philip_mcaleer_glasgow_ac_uk/Documents/Documents/sotl_glossary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{75AEDCF6-18AF-F147-9E71-A81F5CC1F1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0325C26-B76D-4E78-A800-5B3C52C3AEC0}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="6_{BBFCA202-2727-4AB7-88B5-8F226085420C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ABEB6F3-2EAE-4608-AB17-DBB146A0F247}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -212,7 +212,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="74">
   <si>
     <t>Order in publication</t>
   </si>
@@ -389,6 +389,51 @@
   </si>
   <si>
     <t>Draper</t>
+  </si>
+  <si>
+    <t>Anshul</t>
+  </si>
+  <si>
+    <t>Lau</t>
+  </si>
+  <si>
+    <t>Tanya</t>
+  </si>
+  <si>
+    <t>Fernbank</t>
+  </si>
+  <si>
+    <t>Peter</t>
+  </si>
+  <si>
+    <t>Moll</t>
+  </si>
+  <si>
+    <t>Anna Freud Centre</t>
+  </si>
+  <si>
+    <t>Learning Development Advisor, University of Huddersfield and Associate Lecturer in English for Academic Purposes, University College London</t>
+  </si>
+  <si>
+    <t>Technology Enhanced Learning Advisor, University of Reading</t>
+  </si>
+  <si>
+    <t>Katharine</t>
+  </si>
+  <si>
+    <t>Terrell</t>
+  </si>
+  <si>
+    <t>Academic Services, University of Glasgow</t>
+  </si>
+  <si>
+    <t>Valentine</t>
+  </si>
+  <si>
+    <t>Borges</t>
+  </si>
+  <si>
+    <t>Tutor in Science and Humanities, Aberystwyth University</t>
   </si>
 </sst>
 </file>
@@ -500,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -526,6 +571,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1651,9 +1699,13 @@
       <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="7"/>
+      <c r="B13" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
+      <c r="D13" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="E13" s="7" t="b">
         <v>0</v>
       </c>
@@ -1696,7 +1748,9 @@
       <c r="R13" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="S13" s="7"/>
+      <c r="S13" s="12" t="s">
+        <v>65</v>
+      </c>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="8"/>
@@ -1711,9 +1765,13 @@
       <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="7"/>
+      <c r="B14" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+      <c r="D14" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="E14" s="7" t="b">
         <v>0</v>
       </c>
@@ -1756,7 +1814,9 @@
       <c r="R14" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="S14" s="7"/>
+      <c r="S14" s="12" t="s">
+        <v>66</v>
+      </c>
       <c r="T14" s="7"/>
       <c r="U14" s="7"/>
       <c r="V14" s="6"/>
@@ -1771,9 +1831,13 @@
       <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="7"/>
+      <c r="B15" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
+      <c r="D15" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="E15" s="7" t="b">
         <v>0</v>
       </c>
@@ -1816,7 +1880,9 @@
       <c r="R15" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="S15" s="7"/>
+      <c r="S15" s="13" t="s">
+        <v>67</v>
+      </c>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="6"/>
@@ -1831,9 +1897,13 @@
       <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="7"/>
+      <c r="B16" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+      <c r="D16" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="E16" s="7" t="b">
         <v>0</v>
       </c>
@@ -1876,7 +1946,9 @@
       <c r="R16" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="S16" s="7"/>
+      <c r="S16" s="7" t="s">
+        <v>70</v>
+      </c>
       <c r="T16" s="7"/>
       <c r="U16" s="7"/>
       <c r="V16" s="6"/>
@@ -1891,9 +1963,13 @@
       <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="7"/>
+      <c r="B17" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
+      <c r="D17" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="E17" s="7" t="b">
         <v>0</v>
       </c>
@@ -1936,7 +2012,9 @@
       <c r="R17" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="S17" s="7"/>
+      <c r="S17" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
       <c r="V17" s="6"/>
